--- a/business_forms/031_sales_team_daily_report_form--business_forms.xlsx
+++ b/business_forms/031_sales_team_daily_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sales_region</t>
+          <t>sales_region_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sales Region</t>
+          <t>Sales Region 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sales Region</t>
+          <t>Sales Manager Region</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>region_status</t>
+          <t>region_status_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Region Status</t>
+          <t>Region Status 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>region_status</t>
+          <t>region_status_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Region Status</t>
+          <t>Region Status 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sales_amount</t>
+          <t>sales_amount_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sales Amount</t>
+          <t>Sales Amount 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sales_manager_note</t>
+          <t>sales_manager_note_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sales Manager Note</t>
+          <t>Sales Manager Note 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sales_region_choices</t>
+          <t>sales_region_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sales_region_choices</t>
+          <t>sales_region_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_status_choices</t>
+          <t>region_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_status_choices</t>
+          <t>region_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>region_status_choices</t>
+          <t>region_status_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>region_status_choices</t>
+          <t>region_status_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
